--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_depmayores_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_depmayores_a_2023_arica_y_parinacota.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:49</t>
+    <t xml:space="preserve">2026-09-24 01:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -540,10 +540,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3">
@@ -554,10 +554,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.51</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4">
@@ -571,7 +571,7 @@
         <v>-0.26</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5">
@@ -582,10 +582,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6">
@@ -599,7 +599,7 @@
         <v>0.45</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7">
@@ -764,10 +764,10 @@
         <v>23</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>-0.65</v>
+        <v>-0.66</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19">
@@ -806,10 +806,10 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.33</v>
+        <v>0.17</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22">
@@ -823,7 +823,7 @@
         <v>-0.22</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23">
@@ -837,7 +837,7 @@
         <v>0.14</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
